--- a/src/templates/import_template.xlsx
+++ b/src/templates/import_template.xlsx
@@ -32,7 +32,7 @@
     <t>role*</t>
   </si>
   <si>
-    <t>displayName</t>
+    <t>name</t>
   </si>
   <si>
     <t>birthDate</t>
